--- a/config/new-five-tables/source/02_TCIM_十题_教师游戏支持能力多路径Ontology表_V0.2.1_唯一运行版.xlsx
+++ b/config/new-five-tables/source/02_TCIM_十题_教师游戏支持能力多路径Ontology表_V0.2.1_唯一运行版.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rdd3842ed6bbc4880"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RUNTIME_CONTRACT" sheetId="2" r:id="Rf64447c2c2514a4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUESTION_INDEX" sheetId="3" r:id="R89116a23958a449f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DATA" sheetId="4" r:id="Rf21f9408d9154e5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DICTIONARY" sheetId="5" r:id="R0ce33a1ff7564902"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENUMS" sheetId="6" r:id="R5f29ecb72ac24be9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA_SUMMARY" sheetId="7" r:id="Re63ba015384e438f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHANGELOG" sheetId="8" r:id="Rf0a8b8efc076422c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R52ee74e0f6054394"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RUNTIME_CONTRACT" sheetId="2" r:id="R272946904ab64ca5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUESTION_INDEX" sheetId="3" r:id="Re1cdf8a9aa6e456f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DATA" sheetId="4" r:id="Re551752528bd4504"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DICTIONARY" sheetId="5" r:id="R91cc9dd848e642f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENUMS" sheetId="6" r:id="R226554e9670345a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA_SUMMARY" sheetId="7" r:id="R37b41f6da3f4401d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHANGELOG" sheetId="8" r:id="Ra5083c180cf04305"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -11082,7 +11082,7 @@
         <x:v>CAP-Q07-004</x:v>
       </x:c>
       <x:c r="F97" s="14" t="str">
-        <x:v>C05|C10|C11</x:v>
+        <x:v>C05|C06|C10|C11</x:v>
       </x:c>
       <x:c r="G97" s="14" t="str">
         <x:v>GAME_SUPPORT</x:v>
@@ -11186,7 +11186,7 @@
         <x:v>CAP-Q07-004</x:v>
       </x:c>
       <x:c r="F98" s="14" t="str">
-        <x:v>C05|C10|C11</x:v>
+        <x:v>C05|C06|C10|C11</x:v>
       </x:c>
       <x:c r="G98" s="14" t="str">
         <x:v>GAME_SUPPORT</x:v>
@@ -11290,7 +11290,7 @@
         <x:v>CAP-Q07-004</x:v>
       </x:c>
       <x:c r="F99" s="14" t="str">
-        <x:v>C05|C10|C11</x:v>
+        <x:v>C05|C06|C10|C11</x:v>
       </x:c>
       <x:c r="G99" s="14" t="str">
         <x:v>GAME_SUPPORT</x:v>
@@ -16404,7 +16404,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca4e3b4551194830"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21ff66a638ba43c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19201,10 +19201,10 @@
         <x:v>CAPABILITY_NAMESPACE</x:v>
       </x:c>
       <x:c r="D11" t="str">
-        <x:v>修正Q06、Q07题内能力ID与全局能力ID的同名冲突，并显式映射父级能力。</x:v>
+        <x:v>修正Q06、Q07题内能力ID同名冲突；复核表2路径父级与表3能力引用的闭合关系。</x:v>
       </x:c>
       <x:c r="E11" t="str">
-        <x:v>避免题内概念被误当全局画像维度，同时保留多路径专业地图。</x:v>
+        <x:v>避免题内概念被误当全局画像维度，并防止证据绑定到路径之外的画像能力。</x:v>
       </x:c>
       <x:c r="F11" t="str">
         <x:v>项目负责人确认；模拟试验启用</x:v>
